--- a/output/dbc_comparison.xlsx
+++ b/output/dbc_comparison.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Start Bit" sheetId="11" r:id="rId11"/>
     <sheet name="Type &amp; Multiplexer" sheetId="12" r:id="rId12"/>
     <sheet name="Unit" sheetId="13" r:id="rId13"/>
+    <sheet name="Value Descriptions" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Byte Order'!$A$1:$F$2</definedName>
@@ -32,8 +33,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Signal Exists'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Start Bit'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Type &amp; Multiplexer'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Value Descriptions'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Length!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Unit!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
   <si>
     <t>Category</t>
   </si>
@@ -88,6 +90,9 @@
     <t>Unit</t>
   </si>
   <si>
+    <t>Value Descriptions</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -245,6 +250,19 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>Read_Status_Alarms_Cyclic</t>
+  </si>
+  <si>
+    <t>Value Description</t>
+  </si>
+  <si>
+    <t>0x0 = "No alarm"
+0x1 = "Alarm"</t>
+  </si>
+  <si>
+    <t>0x0 = "No alarm"</t>
   </si>
 </sst>
 </file>
@@ -616,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -779,8 +797,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <f>HYPERLINK("#'Value Descriptions'!A1", "Go to 'Value Descriptions'")</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -798,62 +828,62 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -875,62 +905,62 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -952,42 +982,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1009,42 +1039,99 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1066,42 +1153,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1123,62 +1210,62 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1200,102 +1287,102 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1317,42 +1404,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1374,40 +1461,40 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1429,58 +1516,58 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1502,40 +1589,40 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1557,42 +1644,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
